--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127743697</v>
+        <v>136828025</v>
       </c>
       <c r="B3" t="n">
-        <v>79413</v>
+        <v>83463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,38 +807,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411956</v>
+        <v>412384</v>
       </c>
       <c r="R3" t="n">
-        <v>6966544</v>
+        <v>6966150</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,22 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:47</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:47</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,27 +881,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127743697</t>
+          <t>https://artportalen.se/Sighting/136828025</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126348493</v>
+        <v>127743697</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>79413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,37 +909,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6450</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412166</v>
+        <v>411956</v>
       </c>
       <c r="R4" t="n">
-        <v>6966378</v>
+        <v>6966544</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,17 +967,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,24 +997,24 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348493</t>
+          <t>https://artportalen.se/Sighting/127743697</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126348494</v>
+        <v>126348493</v>
       </c>
       <c r="B5" t="n">
         <v>57953</v>
@@ -1054,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411996</v>
+        <v>412166</v>
       </c>
       <c r="R5" t="n">
-        <v>6966281</v>
+        <v>6966378</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,13 +1115,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348494</t>
+          <t>https://artportalen.se/Sighting/126348493</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126348496</v>
+        <v>126348494</v>
       </c>
       <c r="B6" t="n">
         <v>57953</v>
@@ -1161,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>412108</v>
+        <v>411996</v>
       </c>
       <c r="R6" t="n">
-        <v>6966128</v>
+        <v>6966281</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,38 +1222,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348496</t>
+          <t>https://artportalen.se/Sighting/126348494</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126348508</v>
+        <v>126348496</v>
       </c>
       <c r="B7" t="n">
-        <v>97989</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1268,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>411930</v>
+        <v>412108</v>
       </c>
       <c r="R7" t="n">
-        <v>6966300</v>
+        <v>6966128</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,6 +1301,11 @@
           <t>2025-06-30</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1329,7 +1329,313 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/126348496</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126348508</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>411930</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6966300</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/126348508</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136828026</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98221</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>412374</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6966243</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136828024</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>412344</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6966001</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828024</t>
         </is>
       </c>
     </row>
@@ -1341,6 +1647,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136828025</v>
+        <v>127743697</v>
       </c>
       <c r="B3" t="n">
-        <v>83463</v>
+        <v>79413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,34 +807,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412384</v>
+        <v>411956</v>
       </c>
       <c r="R3" t="n">
-        <v>6966150</v>
+        <v>6966544</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,12 +865,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,27 +895,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828025</t>
+          <t>https://artportalen.se/Sighting/127743697</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127743697</v>
+        <v>126348493</v>
       </c>
       <c r="B4" t="n">
-        <v>79413</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,41 +923,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6450</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411956</v>
+        <v>412166</v>
       </c>
       <c r="R4" t="n">
-        <v>6966544</v>
+        <v>6966378</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,22 +977,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:47</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:47</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,24 +1002,24 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127743697</t>
+          <t>https://artportalen.se/Sighting/126348493</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126348493</v>
+        <v>126348494</v>
       </c>
       <c r="B5" t="n">
         <v>57953</v>
@@ -1049,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412166</v>
+        <v>411996</v>
       </c>
       <c r="R5" t="n">
-        <v>6966378</v>
+        <v>6966281</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,13 +1120,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348493</t>
+          <t>https://artportalen.se/Sighting/126348494</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126348494</v>
+        <v>126348496</v>
       </c>
       <c r="B6" t="n">
         <v>57953</v>
@@ -1156,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411996</v>
+        <v>412108</v>
       </c>
       <c r="R6" t="n">
-        <v>6966281</v>
+        <v>6966128</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,38 +1227,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348494</t>
+          <t>https://artportalen.se/Sighting/126348496</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126348496</v>
+        <v>126348508</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>97989</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1263,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>412108</v>
+        <v>411930</v>
       </c>
       <c r="R7" t="n">
-        <v>6966128</v>
+        <v>6966300</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,11 +1306,6 @@
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1329,313 +1329,7 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348496</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>126348508</v>
-      </c>
-      <c r="B8" t="n">
-        <v>97989</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>221941</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Plattlummer</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Lycopodium complanatum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Digerberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>411930</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6966300</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/126348508</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>136828026</v>
-      </c>
-      <c r="B9" t="n">
-        <v>98221</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>221941</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Plattlummer</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Lycopodium complanatum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>412374</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6966243</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828026</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>136828024</v>
-      </c>
-      <c r="B10" t="n">
-        <v>79499</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>412344</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6966001</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828024</t>
         </is>
       </c>
     </row>
@@ -1647,9 +1341,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136828025</v>
       </c>
       <c r="B3" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>136828026</v>
       </c>
       <c r="B9" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>136828024</v>
       </c>
       <c r="B10" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136828025</v>
       </c>
       <c r="B3" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>136828026</v>
       </c>
       <c r="B9" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>136828024</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136828025</v>
       </c>
       <c r="B3" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>136828026</v>
       </c>
       <c r="B9" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>136828024</v>
       </c>
       <c r="B10" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -1440,7 +1440,7 @@
         <v>136828026</v>
       </c>
       <c r="B9" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136828025</v>
+        <v>127743697</v>
       </c>
       <c r="B3" t="n">
-        <v>83470</v>
+        <v>79413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,34 +807,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412384</v>
+        <v>411956</v>
       </c>
       <c r="R3" t="n">
-        <v>6966150</v>
+        <v>6966544</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,12 +865,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,27 +895,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828025</t>
+          <t>https://artportalen.se/Sighting/127743697</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127743697</v>
+        <v>126348493</v>
       </c>
       <c r="B4" t="n">
-        <v>79413</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,41 +923,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6450</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411956</v>
+        <v>412166</v>
       </c>
       <c r="R4" t="n">
-        <v>6966544</v>
+        <v>6966378</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,22 +977,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:47</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:47</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,24 +1002,24 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127743697</t>
+          <t>https://artportalen.se/Sighting/126348493</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126348493</v>
+        <v>126348494</v>
       </c>
       <c r="B5" t="n">
         <v>57953</v>
@@ -1049,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412166</v>
+        <v>411996</v>
       </c>
       <c r="R5" t="n">
-        <v>6966378</v>
+        <v>6966281</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,13 +1120,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348493</t>
+          <t>https://artportalen.se/Sighting/126348494</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126348494</v>
+        <v>126348496</v>
       </c>
       <c r="B6" t="n">
         <v>57953</v>
@@ -1156,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411996</v>
+        <v>412108</v>
       </c>
       <c r="R6" t="n">
-        <v>6966281</v>
+        <v>6966128</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,38 +1227,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348494</t>
+          <t>https://artportalen.se/Sighting/126348496</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126348496</v>
+        <v>126348508</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>97989</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1263,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>412108</v>
+        <v>411930</v>
       </c>
       <c r="R7" t="n">
-        <v>6966128</v>
+        <v>6966300</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,11 +1306,6 @@
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1329,313 +1329,7 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348496</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>126348508</v>
-      </c>
-      <c r="B8" t="n">
-        <v>97989</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>221941</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Plattlummer</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Lycopodium complanatum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Digerberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>411930</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6966300</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/126348508</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>136828026</v>
-      </c>
-      <c r="B9" t="n">
-        <v>98236</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>221941</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Plattlummer</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Lycopodium complanatum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>412374</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6966243</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828026</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>136828024</v>
-      </c>
-      <c r="B10" t="n">
-        <v>79506</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>412344</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6966001</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828024</t>
         </is>
       </c>
     </row>
@@ -1647,9 +1341,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127743697</v>
+        <v>136828025</v>
       </c>
       <c r="B3" t="n">
-        <v>79413</v>
+        <v>83474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,38 +807,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411956</v>
+        <v>412384</v>
       </c>
       <c r="R3" t="n">
-        <v>6966544</v>
+        <v>6966150</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,22 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:47</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:47</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,27 +881,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127743697</t>
+          <t>https://artportalen.se/Sighting/136828025</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126348493</v>
+        <v>127743697</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>79413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,37 +909,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6450</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412166</v>
+        <v>411956</v>
       </c>
       <c r="R4" t="n">
-        <v>6966378</v>
+        <v>6966544</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,17 +967,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,24 +997,24 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348493</t>
+          <t>https://artportalen.se/Sighting/127743697</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126348494</v>
+        <v>126348493</v>
       </c>
       <c r="B5" t="n">
         <v>57953</v>
@@ -1054,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411996</v>
+        <v>412166</v>
       </c>
       <c r="R5" t="n">
-        <v>6966281</v>
+        <v>6966378</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,13 +1115,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348494</t>
+          <t>https://artportalen.se/Sighting/126348493</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126348496</v>
+        <v>126348494</v>
       </c>
       <c r="B6" t="n">
         <v>57953</v>
@@ -1161,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>412108</v>
+        <v>411996</v>
       </c>
       <c r="R6" t="n">
-        <v>6966128</v>
+        <v>6966281</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,38 +1222,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348496</t>
+          <t>https://artportalen.se/Sighting/126348494</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126348508</v>
+        <v>126348496</v>
       </c>
       <c r="B7" t="n">
-        <v>97989</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1268,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>411930</v>
+        <v>412108</v>
       </c>
       <c r="R7" t="n">
-        <v>6966300</v>
+        <v>6966128</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,6 +1301,11 @@
           <t>2025-06-30</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1329,7 +1329,313 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/126348496</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126348508</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>411930</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6966300</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/126348508</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136828026</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98240</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>412374</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6966243</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136828024</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79508</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>412344</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6966001</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828024</t>
         </is>
       </c>
     </row>
@@ -1341,6 +1647,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136828025</v>
+        <v>127743697</v>
       </c>
       <c r="B3" t="n">
-        <v>83474</v>
+        <v>79413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,34 +807,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412384</v>
+        <v>411956</v>
       </c>
       <c r="R3" t="n">
-        <v>6966150</v>
+        <v>6966544</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,12 +865,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,27 +895,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828025</t>
+          <t>https://artportalen.se/Sighting/127743697</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127743697</v>
+        <v>126348493</v>
       </c>
       <c r="B4" t="n">
-        <v>79413</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,41 +923,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6450</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411956</v>
+        <v>412166</v>
       </c>
       <c r="R4" t="n">
-        <v>6966544</v>
+        <v>6966378</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,22 +977,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:47</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:47</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,24 +1002,24 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127743697</t>
+          <t>https://artportalen.se/Sighting/126348493</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126348493</v>
+        <v>126348494</v>
       </c>
       <c r="B5" t="n">
         <v>57953</v>
@@ -1049,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412166</v>
+        <v>411996</v>
       </c>
       <c r="R5" t="n">
-        <v>6966378</v>
+        <v>6966281</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,13 +1120,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348493</t>
+          <t>https://artportalen.se/Sighting/126348494</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126348494</v>
+        <v>126348496</v>
       </c>
       <c r="B6" t="n">
         <v>57953</v>
@@ -1156,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411996</v>
+        <v>412108</v>
       </c>
       <c r="R6" t="n">
-        <v>6966281</v>
+        <v>6966128</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,38 +1227,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348494</t>
+          <t>https://artportalen.se/Sighting/126348496</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126348496</v>
+        <v>126348508</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>97989</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1263,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>412108</v>
+        <v>411930</v>
       </c>
       <c r="R7" t="n">
-        <v>6966128</v>
+        <v>6966300</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,11 +1306,6 @@
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1329,313 +1329,7 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348496</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>126348508</v>
-      </c>
-      <c r="B8" t="n">
-        <v>97989</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>221941</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Plattlummer</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Lycopodium complanatum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Digerberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>411930</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6966300</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/126348508</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>136828026</v>
-      </c>
-      <c r="B9" t="n">
-        <v>98240</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>221941</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Plattlummer</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Lycopodium complanatum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>412374</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6966243</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828026</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>136828024</v>
-      </c>
-      <c r="B10" t="n">
-        <v>79508</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>412344</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6966001</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828024</t>
         </is>
       </c>
     </row>
@@ -1647,9 +1341,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127743697</v>
+        <v>136828025</v>
       </c>
       <c r="B3" t="n">
-        <v>79413</v>
+        <v>83476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,38 +807,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411956</v>
+        <v>412384</v>
       </c>
       <c r="R3" t="n">
-        <v>6966544</v>
+        <v>6966150</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,22 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:47</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:47</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,27 +881,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127743697</t>
+          <t>https://artportalen.se/Sighting/136828025</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126348493</v>
+        <v>127743697</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>79413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,37 +909,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6450</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412166</v>
+        <v>411956</v>
       </c>
       <c r="R4" t="n">
-        <v>6966378</v>
+        <v>6966544</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,17 +967,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,24 +997,24 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348493</t>
+          <t>https://artportalen.se/Sighting/127743697</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126348494</v>
+        <v>126348493</v>
       </c>
       <c r="B5" t="n">
         <v>57953</v>
@@ -1054,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411996</v>
+        <v>412166</v>
       </c>
       <c r="R5" t="n">
-        <v>6966281</v>
+        <v>6966378</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,13 +1115,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348494</t>
+          <t>https://artportalen.se/Sighting/126348493</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126348496</v>
+        <v>126348494</v>
       </c>
       <c r="B6" t="n">
         <v>57953</v>
@@ -1161,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>412108</v>
+        <v>411996</v>
       </c>
       <c r="R6" t="n">
-        <v>6966128</v>
+        <v>6966281</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,38 +1222,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348496</t>
+          <t>https://artportalen.se/Sighting/126348494</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126348508</v>
+        <v>126348496</v>
       </c>
       <c r="B7" t="n">
-        <v>97989</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1268,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>411930</v>
+        <v>412108</v>
       </c>
       <c r="R7" t="n">
-        <v>6966300</v>
+        <v>6966128</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,6 +1301,11 @@
           <t>2025-06-30</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1329,7 +1329,313 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/126348496</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126348508</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>411930</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6966300</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/126348508</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136828026</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98244</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>412374</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6966243</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136828024</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79511</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>412344</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6966001</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828024</t>
         </is>
       </c>
     </row>
@@ -1341,6 +1647,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136828025</v>
       </c>
       <c r="B3" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>136828026</v>
       </c>
       <c r="B9" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>136828024</v>
       </c>
       <c r="B10" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136828025</v>
       </c>
       <c r="B3" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>136828026</v>
       </c>
       <c r="B9" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>136828024</v>
       </c>
       <c r="B10" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136828025</v>
       </c>
       <c r="B3" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>136828026</v>
       </c>
       <c r="B9" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136828025</v>
       </c>
       <c r="B3" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>136828026</v>
       </c>
       <c r="B9" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>136828024</v>
       </c>
       <c r="B10" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -1440,7 +1440,7 @@
         <v>136828026</v>
       </c>
       <c r="B9" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136828025</v>
       </c>
       <c r="B3" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>136828026</v>
       </c>
       <c r="B9" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>136828024</v>
       </c>
       <c r="B10" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -1440,7 +1440,7 @@
         <v>136828026</v>
       </c>
       <c r="B9" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136828025</v>
       </c>
       <c r="B3" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>136828026</v>
       </c>
       <c r="B9" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>136828024</v>
       </c>
       <c r="B10" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136828025</v>
       </c>
       <c r="B3" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>136828026</v>
       </c>
       <c r="B9" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>136828024</v>
       </c>
       <c r="B10" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
